--- a/data/Liste_DOI_template.xlsx
+++ b/data/Liste_DOI_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hari1996\Documents\GitHub\IBG_repository\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DCAAEB-E7CB-49C5-B12F-E78FC4F79300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14497BD8-862A-49D5-8BBA-4AD279D5B187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23340" yWindow="15990" windowWidth="19755" windowHeight="10410" xr2:uid="{798CB5EC-8258-4D98-A9DC-C3418B63B6C8}"/>
+    <workbookView xWindow="-23685" yWindow="15645" windowWidth="19755" windowHeight="10410" xr2:uid="{798CB5EC-8258-4D98-A9DC-C3418B63B6C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
   <si>
     <t>id</t>
   </si>
@@ -79,6 +79,15 @@
   </si>
   <si>
     <t>0000-0000-0000-0000</t>
+  </si>
+  <si>
+    <t>pdf_filename</t>
+  </si>
+  <si>
+    <t>Paper_1_Muster 1.pdf</t>
+  </si>
+  <si>
+    <t>Paper_2_Muster 2.pdf</t>
   </si>
 </sst>
 </file>
@@ -454,7 +463,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1"/>
@@ -467,7 +476,7 @@
     <col min="8" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -489,8 +498,11 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="H1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -512,8 +524,11 @@
       <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -535,8 +550,11 @@
       <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -558,8 +576,11 @@
       <c r="G4" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="H4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -581,8 +602,11 @@
       <c r="G5" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="H5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -602,8 +626,11 @@
       <c r="G6" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="H6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -623,8 +650,11 @@
       <c r="G7" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="H7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -643,6 +673,9 @@
       </c>
       <c r="G8" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
